--- a/dieu tri.xlsx
+++ b/dieu tri.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive - MSFT\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB907FC5-6AC6-436F-9418-B1902A0837F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA76208-3407-49E4-ACDE-B8019BD12FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33255" yWindow="4440" windowWidth="20085" windowHeight="8865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -615,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -685,7 +685,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -693,19 +692,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -965,45 +968,45 @@
         <v>51</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5" t="s">
-        <v>57</v>
+        <v>121</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="E2">
-        <v>10.4068769</v>
+        <v>10.8187959</v>
       </c>
       <c r="F2">
-        <v>106.9418831</v>
+        <v>106.6805361</v>
       </c>
       <c r="G2" s="1">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
-        <v>51</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>108</v>
+      <c r="A3" s="3">
+        <v>72</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>142</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>56</v>
+        <v>17</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>10.6798705</v>
+        <v>11.2583871</v>
       </c>
       <c r="F3">
-        <v>106.7478354</v>
+        <v>106.60756689999999</v>
       </c>
       <c r="G3" s="1">
-        <v>380</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1012,123 +1015,109 @@
       <c r="A4" s="7">
         <v>51</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="B4" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
       <c r="E4">
-        <v>10.6913866</v>
+        <v>10.779844499999999</v>
       </c>
       <c r="F4">
-        <v>106.5862588</v>
+        <v>106.68180719999999</v>
       </c>
       <c r="G4" s="1">
-        <v>1943</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>51</v>
+      <c r="A5" s="18">
+        <v>61</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>49</v>
+        <v>131</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>10.7279537</v>
+        <v>10.737691399999999</v>
       </c>
       <c r="F5">
-        <v>106.6074327</v>
+        <v>106.726889</v>
       </c>
       <c r="G5" s="1">
-        <v>1332</v>
+        <v>36</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>51</v>
+      <c r="A6" s="18">
+        <v>61</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>6</v>
+        <v>132</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="E6">
-        <v>10.737691399999999</v>
+        <v>10.756396000000001</v>
       </c>
       <c r="F6">
-        <v>106.726889</v>
+        <v>106.682446</v>
       </c>
       <c r="G6" s="1">
-        <v>1253</v>
+        <v>38</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>7</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
       <c r="E7">
-        <v>10.749357</v>
+        <v>10.843193400000001</v>
       </c>
       <c r="F7">
-        <v>106.683744</v>
+        <v>106.67462020000001</v>
       </c>
       <c r="G7" s="1">
-        <v>2441</v>
+        <v>44</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>51</v>
+      <c r="A8" s="18">
+        <v>61</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
+        <v>130</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="E8">
-        <v>10.752404</v>
+        <v>10.879506900000001</v>
       </c>
       <c r="F8">
-        <v>106.68212269999999</v>
+        <v>106.6779872</v>
       </c>
       <c r="G8" s="1">
-        <v>1503</v>
+        <v>52</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1138,47 +1127,41 @@
         <v>51</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>58</v>
+        <v>116</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="E9">
-        <v>10.7531734</v>
+        <v>10.7814918</v>
       </c>
       <c r="F9">
-        <v>106.6784356</v>
+        <v>106.7028325</v>
       </c>
       <c r="G9" s="1">
-        <v>2326</v>
+        <v>71</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>44</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10">
-        <v>10.754125999999999</v>
+        <v>10.910496800000001</v>
       </c>
       <c r="F10">
-        <v>106.63513</v>
+        <v>106.7720695</v>
       </c>
       <c r="G10" s="1">
-        <v>1458</v>
+        <v>78</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1188,11 +1171,13 @@
         <v>51</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="10" t="s">
-        <v>40</v>
+        <v>120</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="E11">
         <v>10.754680199999999</v>
@@ -1201,57 +1186,55 @@
         <v>106.6586923</v>
       </c>
       <c r="G11" s="1">
-        <v>857</v>
+        <v>86</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>51</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>89</v>
+      <c r="A12" s="3">
+        <v>72</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="E12">
-        <v>10.756396000000001</v>
+        <v>11.1496355</v>
       </c>
       <c r="F12">
-        <v>106.682446</v>
+        <v>106.8429288</v>
       </c>
       <c r="G12" s="1">
-        <v>1285</v>
+        <v>87</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>51</v>
+      <c r="A13" s="18">
+        <v>61</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>5</v>
+        <v>129</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="E13">
-        <v>10.756917</v>
+        <v>11.1639348</v>
       </c>
       <c r="F13">
-        <v>106.7180599</v>
+        <v>106.59009639999999</v>
       </c>
       <c r="G13" s="1">
-        <v>1840</v>
+        <v>131</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1261,45 +1244,41 @@
         <v>51</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>23</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C14" s="6"/>
       <c r="D14" s="5" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E14">
-        <v>10.763468</v>
+        <v>10.591458100000001</v>
       </c>
       <c r="F14">
-        <v>106.649007</v>
+        <v>106.8149227</v>
       </c>
       <c r="G14" s="1">
-        <v>2930</v>
+        <v>139</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="10" t="s">
-        <v>41</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
       <c r="E15">
-        <v>10.769371</v>
+        <v>10.975711</v>
       </c>
       <c r="F15">
-        <v>106.67093300000001</v>
+        <v>106.501437</v>
       </c>
       <c r="G15" s="1">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1309,47 +1288,43 @@
         <v>51</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>4</v>
+        <v>115</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="E16">
-        <v>10.7744357</v>
+        <v>10.3924834</v>
       </c>
       <c r="F16">
-        <v>106.6838133</v>
+        <v>107.127064</v>
       </c>
       <c r="G16" s="1">
-        <v>2877</v>
+        <v>174</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
-        <v>51</v>
+      <c r="A17" s="18">
+        <v>61</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>52</v>
+        <v>128</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="E17">
-        <v>10.7747016</v>
+        <v>11.0854347</v>
       </c>
       <c r="F17">
-        <v>106.64813220000001</v>
+        <v>106.77769259999999</v>
       </c>
       <c r="G17" s="1">
-        <v>2979</v>
+        <v>191</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1359,20 +1334,20 @@
         <v>51</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E18">
-        <v>10.779844499999999</v>
+        <v>12.060221200000001</v>
       </c>
       <c r="F18">
-        <v>106.68180719999999</v>
+        <v>107.10738720000001</v>
       </c>
       <c r="G18" s="1">
-        <v>1662</v>
+        <v>191</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1382,22 +1357,20 @@
         <v>51</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>8</v>
+        <v>111</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="E19">
-        <v>10.7805435</v>
+        <v>10.8644079</v>
       </c>
       <c r="F19">
-        <v>106.6715413</v>
+        <v>106.7455702</v>
       </c>
       <c r="G19" s="1">
-        <v>2038</v>
+        <v>198</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1406,71 +1379,69 @@
       <c r="A20" s="7">
         <v>51</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <v>10.781197199999999</v>
-      </c>
-      <c r="F20">
-        <v>106.75778560000001</v>
+      <c r="B20" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="1">
+        <v>10.797376</v>
+      </c>
+      <c r="F20" s="1">
+        <v>106.6599927</v>
       </c>
       <c r="G20" s="1">
-        <v>1121</v>
+        <v>267</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <v>51</v>
+      <c r="A21" s="3">
+        <v>72</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="16" t="s">
-        <v>60</v>
+        <v>140</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="E21">
-        <v>10.7814918</v>
+        <v>10.6913866</v>
       </c>
       <c r="F21">
-        <v>106.7028325</v>
+        <v>106.5862588</v>
       </c>
       <c r="G21" s="1">
-        <v>191</v>
+        <v>295</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
-        <v>51</v>
+      <c r="A22" s="3">
+        <v>72</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>78</v>
       </c>
       <c r="E22">
-        <v>10.7903652</v>
+        <v>10.756917</v>
       </c>
       <c r="F22">
-        <v>106.69001780000001</v>
+        <v>106.7180599</v>
       </c>
       <c r="G22" s="1">
-        <v>1440</v>
+        <v>299</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1479,23 +1450,19 @@
       <c r="A23" s="7">
         <v>51</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="B23" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4"/>
       <c r="E23">
-        <v>10.791648</v>
+        <v>10.752404</v>
       </c>
       <c r="F23">
-        <v>106.6697379</v>
+        <v>106.68212269999999</v>
       </c>
       <c r="G23" s="1">
-        <v>1003</v>
+        <v>301</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1505,143 +1472,143 @@
         <v>51</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E24">
-        <v>10.792902099999999</v>
+        <v>10.7744357</v>
       </c>
       <c r="F24">
-        <v>106.62057110000001</v>
+        <v>106.6838133</v>
       </c>
       <c r="G24" s="1">
-        <v>1243</v>
+        <v>380</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
-        <v>51</v>
+      <c r="A25" s="3">
+        <v>72</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="4" t="s">
-        <v>65</v>
+        <v>138</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="E25">
-        <v>10.7967716</v>
+        <v>11.2894361</v>
       </c>
       <c r="F25">
-        <v>106.6627697</v>
+        <v>106.7949788</v>
       </c>
       <c r="G25" s="1">
-        <v>4</v>
+        <v>534</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
-        <v>51</v>
+      <c r="A26" s="3">
+        <v>72</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>55</v>
+        <v>14</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>80</v>
       </c>
       <c r="E26">
-        <v>10.804119999999999</v>
+        <v>11.2879635</v>
       </c>
       <c r="F26">
-        <v>106.710095</v>
+        <v>106.3913776</v>
       </c>
       <c r="G26" s="1">
-        <v>2345</v>
+        <v>625</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
-        <v>51</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="17" t="s">
-        <v>62</v>
+      <c r="A27" s="18">
+        <v>61</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="E27">
-        <v>10.8187959</v>
+        <v>10.791648</v>
       </c>
       <c r="F27">
-        <v>106.6805361</v>
+        <v>106.6697379</v>
       </c>
       <c r="G27" s="1">
-        <v>71</v>
+        <v>705</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
-        <v>51</v>
+      <c r="A28" s="3">
+        <v>72</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="E28">
-        <v>10.8424069</v>
+        <v>10.9781475</v>
       </c>
       <c r="F28">
-        <v>106.82139119999999</v>
+        <v>106.65141079999999</v>
       </c>
       <c r="G28" s="1">
-        <v>1175</v>
+        <v>786</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
-        <v>51</v>
+      <c r="A29" s="18">
+        <v>61</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>51</v>
+        <v>125</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="E29">
-        <v>10.843193400000001</v>
+        <v>10.792902099999999</v>
       </c>
       <c r="F29">
-        <v>106.67462020000001</v>
+        <v>106.62057110000001</v>
       </c>
       <c r="G29" s="1">
-        <v>2806</v>
+        <v>829</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1651,72 +1618,66 @@
         <v>51</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>54</v>
+        <v>113</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="E30">
-        <v>10.853793400000001</v>
+        <v>10.769371</v>
       </c>
       <c r="F30">
-        <v>106.7532921</v>
+        <v>106.67093300000001</v>
       </c>
       <c r="G30" s="1">
-        <v>1841</v>
+        <v>857</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
-        <v>51</v>
+      <c r="A31" s="18">
+        <v>61</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>64</v>
+        <v>123</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="E31">
-        <v>10.854276799999999</v>
+        <v>10.7805435</v>
       </c>
       <c r="F31">
-        <v>106.7512353</v>
+        <v>106.6715413</v>
       </c>
       <c r="G31" s="1">
-        <v>86</v>
+        <v>877</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
-        <v>51</v>
+      <c r="A32" s="18">
+        <v>61</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>59</v>
+        <v>126</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="E32">
-        <v>10.8644079</v>
+        <v>10.7747016</v>
       </c>
       <c r="F32">
-        <v>106.7455702</v>
+        <v>106.64813220000001</v>
       </c>
       <c r="G32" s="1">
-        <v>2999</v>
+        <v>959</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1726,22 +1687,20 @@
         <v>51</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>10</v>
+        <v>114</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="E33">
-        <v>10.8689663</v>
+        <v>11.034454</v>
       </c>
       <c r="F33">
-        <v>106.6001974</v>
+        <v>106.5230191</v>
       </c>
       <c r="G33" s="1">
-        <v>1656</v>
+        <v>995</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1759,11 +1718,11 @@
       <c r="D34" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E34">
-        <v>10.879506900000001</v>
-      </c>
-      <c r="F34">
-        <v>106.6779872</v>
+      <c r="E34" s="1">
+        <v>10.59721</v>
+      </c>
+      <c r="F34" s="1">
+        <v>106.9759614</v>
       </c>
       <c r="G34" s="1">
         <v>999</v>
@@ -1775,46 +1734,46 @@
       <c r="A35" s="7">
         <v>51</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>105</v>
+      <c r="B35" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E35">
-        <v>10.975711</v>
+        <v>10.853793400000001</v>
       </c>
       <c r="F35">
-        <v>106.501437</v>
+        <v>106.7532921</v>
       </c>
       <c r="G35" s="1">
-        <v>1369</v>
+        <v>1003</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
-        <v>51</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="28" t="s">
+      <c r="A36" s="18">
         <v>61</v>
       </c>
+      <c r="B36" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="E36">
-        <v>11.034454</v>
+        <v>10.7903652</v>
       </c>
       <c r="F36">
-        <v>106.5230191</v>
+        <v>106.69001780000001</v>
       </c>
       <c r="G36" s="1">
-        <v>174</v>
+        <v>1100</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1824,112 +1783,122 @@
         <v>51</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9" t="s">
-        <v>42</v>
+        <v>86</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>12.060221200000001</v>
+        <v>10.763468</v>
       </c>
       <c r="F37">
-        <v>107.10738720000001</v>
+        <v>106.649007</v>
       </c>
       <c r="G37" s="1">
-        <v>995</v>
+        <v>1121</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="18">
-        <v>61</v>
+      <c r="A38" s="7">
+        <v>51</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38">
-        <v>10.9032637</v>
-      </c>
-      <c r="F38">
-        <v>106.7062672</v>
+        <v>103</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10.833179100000001</v>
+      </c>
+      <c r="F38" s="1">
+        <v>106.7754443</v>
       </c>
       <c r="G38" s="1">
-        <v>1293</v>
+        <v>1175</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="18">
-        <v>61</v>
+      <c r="A39" s="7">
+        <v>51</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3" t="s">
-        <v>76</v>
+        <v>101</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="E39">
-        <v>10.9083784</v>
+        <v>10.8424069</v>
       </c>
       <c r="F39">
-        <v>106.6923918</v>
+        <v>106.82139119999999</v>
       </c>
       <c r="G39" s="1">
-        <v>38</v>
+        <v>1243</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="18">
-        <v>61</v>
+      <c r="A40" s="7">
+        <v>51</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>10.910496800000001</v>
+        <v>10.8689663</v>
       </c>
       <c r="F40">
-        <v>106.7720695</v>
+        <v>106.6001974</v>
       </c>
       <c r="G40" s="1">
-        <v>877</v>
+        <v>1253</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="18">
-        <v>61</v>
+      <c r="A41" s="7">
+        <v>51</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3" t="s">
-        <v>67</v>
+        <v>89</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="E41">
-        <v>10.9781475</v>
+        <v>10.754125999999999</v>
       </c>
       <c r="F41">
-        <v>106.65141079999999</v>
+        <v>106.63513</v>
       </c>
       <c r="G41" s="1">
-        <v>959</v>
+        <v>1285</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1938,175 +1907,183 @@
       <c r="A42" s="18">
         <v>61</v>
       </c>
-      <c r="B42" s="32" t="s">
-        <v>145</v>
+      <c r="B42" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E42">
-        <v>10.99512</v>
+        <v>10.9032637</v>
       </c>
       <c r="F42">
-        <v>106.65606699999999</v>
+        <v>106.7062672</v>
       </c>
       <c r="G42" s="1">
-        <v>705</v>
+        <v>1293</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="18">
-        <v>61</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3" t="s">
-        <v>71</v>
+      <c r="A43" s="7">
+        <v>51</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="E43">
-        <v>11.0854347</v>
+        <v>10.804119999999999</v>
       </c>
       <c r="F43">
-        <v>106.77769259999999</v>
+        <v>106.710095</v>
       </c>
       <c r="G43" s="1">
-        <v>829</v>
+        <v>1332</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="18">
-        <v>61</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3" t="s">
-        <v>75</v>
+      <c r="A44" s="7">
+        <v>51</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="E44">
-        <v>11.1496355</v>
+        <v>10.7279537</v>
       </c>
       <c r="F44">
-        <v>106.8429288</v>
+        <v>106.6074327</v>
       </c>
       <c r="G44" s="1">
-        <v>36</v>
+        <v>1369</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="18">
-        <v>61</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3" t="s">
-        <v>70</v>
+      <c r="A45" s="7">
+        <v>51</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>11.1639348</v>
+        <v>10.4068769</v>
       </c>
       <c r="F45">
-        <v>106.59009639999999</v>
+        <v>106.9418831</v>
       </c>
       <c r="G45" s="1">
-        <v>1100</v>
+        <v>1440</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="18">
-        <v>61</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46">
-        <v>11.2583871</v>
-      </c>
-      <c r="F46">
-        <v>106.60756689999999</v>
+      <c r="A46" s="7">
+        <v>51</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="1">
+        <v>11.242782200000001</v>
+      </c>
+      <c r="F46" s="1">
+        <v>106.73288789999999</v>
       </c>
       <c r="G46" s="1">
-        <v>52</v>
+        <v>1458</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="18">
-        <v>61</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>128</v>
+      <c r="A47" s="7">
+        <v>51</v>
+      </c>
+      <c r="B47" s="29" t="s">
+        <v>118</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="3" t="s">
-        <v>72</v>
-      </c>
+      <c r="D47" s="4"/>
       <c r="E47">
-        <v>11.2879635</v>
+        <v>10.854276799999999</v>
       </c>
       <c r="F47">
-        <v>106.3913776</v>
+        <v>106.7512353</v>
       </c>
       <c r="G47" s="1">
-        <v>191</v>
+        <v>1503</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="18">
-        <v>61</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3" t="s">
-        <v>73</v>
+      <c r="A48" s="7">
+        <v>51</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>11.2894361</v>
+        <v>10.99512</v>
       </c>
       <c r="F48">
-        <v>106.7949788</v>
+        <v>106.65606699999999</v>
       </c>
       <c r="G48" s="1">
-        <v>131</v>
+        <v>1503</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
-        <v>72</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>142</v>
+      <c r="A49" s="7">
+        <v>51</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="30" t="s">
-        <v>82</v>
+        <v>34</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="E49" s="1">
         <v>8.6884721000000003</v>
@@ -2115,157 +2092,155 @@
         <v>106.5955307</v>
       </c>
       <c r="G49" s="1">
-        <v>17</v>
+        <v>1656</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
-        <v>72</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="33" t="s">
-        <v>79</v>
+      <c r="A50" s="7">
+        <v>51</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="E50">
-        <v>10.367577300000001</v>
+        <v>10.7967716</v>
       </c>
       <c r="F50">
-        <v>107.07491640000001</v>
+        <v>106.6627697</v>
       </c>
       <c r="G50" s="1">
-        <v>534</v>
+        <v>1662</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
-        <v>72</v>
-      </c>
-      <c r="B51" s="26" t="s">
-        <v>137</v>
+      <c r="A51" s="7">
+        <v>51</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>88</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="E51">
-        <v>10.3924834</v>
+        <v>10.6798705</v>
       </c>
       <c r="F51">
-        <v>107.127064</v>
+        <v>106.7478354</v>
       </c>
       <c r="G51" s="1">
-        <v>299</v>
+        <v>1840</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
-        <v>72</v>
-      </c>
-      <c r="B52" s="26" t="s">
-        <v>136</v>
+      <c r="A52" s="7">
+        <v>51</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52">
-        <v>10.509597100000001</v>
-      </c>
-      <c r="F52">
-        <v>107.19429890000001</v>
+        <v>32</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="1">
+        <v>11.4531648</v>
+      </c>
+      <c r="F52" s="1">
+        <v>106.7753458</v>
       </c>
       <c r="G52" s="1">
-        <v>786</v>
+        <v>1841</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
-        <v>72</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>139</v>
+      <c r="A53" s="7">
+        <v>51</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>106</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E53" s="1">
-        <v>10.597046799999999</v>
-      </c>
-      <c r="F53" s="1">
-        <v>107.05596540000001</v>
+        <v>25</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>10.781197199999999</v>
+      </c>
+      <c r="F53">
+        <v>106.75778560000001</v>
       </c>
       <c r="G53" s="1">
-        <v>625</v>
+        <v>1943</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3">
-        <v>72</v>
-      </c>
-      <c r="B54" s="26" t="s">
-        <v>140</v>
+      <c r="A54" s="7">
+        <v>51</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>95</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" s="1">
-        <v>10.59721</v>
-      </c>
-      <c r="F54" s="1">
-        <v>106.9759614</v>
+        <v>22</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54">
+        <v>10.367577300000001</v>
+      </c>
+      <c r="F54">
+        <v>107.07491640000001</v>
       </c>
       <c r="G54" s="1">
-        <v>295</v>
+        <v>2038</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
-        <v>72</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>143</v>
+      <c r="A55" s="7">
+        <v>51</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E55" s="1">
-        <v>10.697192599999999</v>
-      </c>
-      <c r="F55" s="1">
-        <v>107.2904827</v>
+        <v>37</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55">
+        <v>10.509597100000001</v>
+      </c>
+      <c r="F55">
+        <v>107.19429890000001</v>
       </c>
       <c r="G55" s="1">
-        <v>87</v>
+        <v>2326</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -2274,19 +2249,23 @@
       <c r="A56" s="7">
         <v>51</v>
       </c>
-      <c r="B56" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="4"/>
+      <c r="B56" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="E56" s="1">
-        <v>10.797376</v>
+        <v>10.767180400000001</v>
       </c>
       <c r="F56" s="1">
-        <v>106.6599927</v>
+        <v>106.6643491</v>
       </c>
       <c r="G56" s="1">
-        <v>1503</v>
+        <v>2345</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -2295,11 +2274,15 @@
       <c r="A57" s="7">
         <v>51</v>
       </c>
-      <c r="B57" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="4"/>
+      <c r="B57" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="E57" s="1">
         <v>10.7457928</v>
       </c>
@@ -2307,7 +2290,7 @@
         <v>106.66039960000001</v>
       </c>
       <c r="G57" s="1">
-        <v>301</v>
+        <v>2441</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -2316,19 +2299,23 @@
       <c r="A58" s="7">
         <v>51</v>
       </c>
-      <c r="B58" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="4"/>
+      <c r="B58" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E58" s="1">
-        <v>10.8675332</v>
+        <v>10.597046799999999</v>
       </c>
       <c r="F58" s="1">
-        <v>106.63021790000001</v>
+        <v>107.05596540000001</v>
       </c>
       <c r="G58" s="1">
-        <v>267</v>
+        <v>2806</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -2337,82 +2324,98 @@
       <c r="A59" s="7">
         <v>51</v>
       </c>
-      <c r="B59" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="4"/>
+      <c r="B59" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="E59" s="1">
-        <v>10.767180400000001</v>
+        <v>10.8675332</v>
       </c>
       <c r="F59" s="1">
-        <v>106.6643491</v>
+        <v>106.63021790000001</v>
       </c>
       <c r="G59" s="1">
-        <v>21</v>
+        <v>2877</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="1">
-        <v>11.4531648</v>
-      </c>
-      <c r="F60" s="1">
-        <v>106.7753458</v>
+        <v>94</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60">
+        <v>10.9083784</v>
+      </c>
+      <c r="F60">
+        <v>106.6923918</v>
       </c>
       <c r="G60" s="1">
-        <v>78</v>
+        <v>2930</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="E61" s="1">
-        <v>11.242782200000001</v>
+        <v>10.5388123</v>
       </c>
       <c r="F61" s="1">
-        <v>106.73288789999999</v>
+        <v>107.4099504</v>
       </c>
       <c r="G61" s="1">
-        <v>44</v>
+        <v>2979</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="1">
-        <v>10.5388123</v>
-      </c>
-      <c r="F62" s="1">
-        <v>107.4099504</v>
+        <v>112</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E62">
+        <v>10.7531734</v>
+      </c>
+      <c r="F62">
+        <v>106.6784356</v>
       </c>
       <c r="G62" s="1">
-        <v>147</v>
+        <v>2999</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -12494,9 +12497,13 @@
       <c r="I978" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D40" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G62" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">
+      <sortCondition ref="G1:G62"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">
-    <sortCondition ref="A1:A62"/>
+    <sortCondition ref="G1:G62"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dieu tri.xlsx
+++ b/dieu tri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive - MSFT\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA76208-3407-49E4-ACDE-B8019BD12FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C125666-A928-4F94-AE34-956F7B6DA343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33255" yWindow="4440" windowWidth="20085" windowHeight="8865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -695,22 +695,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -987,26 +984,22 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>72</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>82</v>
-      </c>
+      <c r="A3" s="7">
+        <v>51</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
       <c r="E3">
-        <v>11.2583871</v>
+        <v>10.779844499999999</v>
       </c>
       <c r="F3">
-        <v>106.60756689999999</v>
+        <v>106.68180719999999</v>
       </c>
       <c r="G3" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1015,109 +1008,115 @@
       <c r="A4" s="7">
         <v>51</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
+      <c r="B4" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="17" t="s">
+        <v>62</v>
+      </c>
       <c r="E4">
-        <v>10.779844499999999</v>
+        <v>10.7814918</v>
       </c>
       <c r="F4">
-        <v>106.68180719999999</v>
+        <v>106.7028325</v>
       </c>
       <c r="G4" s="1">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18">
-        <v>61</v>
+      <c r="A5" s="7">
+        <v>51</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>75</v>
+        <v>120</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="E5">
-        <v>10.737691399999999</v>
+        <v>10.754680199999999</v>
       </c>
       <c r="F5">
-        <v>106.726889</v>
+        <v>106.6586923</v>
       </c>
       <c r="G5" s="1">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
-        <v>61</v>
+      <c r="A6" s="7">
+        <v>51</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>76</v>
+        <v>109</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="E6">
-        <v>10.756396000000001</v>
+        <v>10.591458100000001</v>
       </c>
       <c r="F6">
-        <v>106.682446</v>
+        <v>106.8149227</v>
       </c>
       <c r="G6" s="1">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
+        <v>51</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
       <c r="E7">
-        <v>10.843193400000001</v>
+        <v>10.3924834</v>
       </c>
       <c r="F7">
-        <v>106.67462020000001</v>
+        <v>107.127064</v>
       </c>
       <c r="G7" s="1">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
-        <v>61</v>
+      <c r="A8" s="7">
+        <v>51</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>110</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="E8">
-        <v>10.879506900000001</v>
+        <v>12.060221200000001</v>
       </c>
       <c r="F8">
-        <v>106.6779872</v>
+        <v>107.10738720000001</v>
       </c>
       <c r="G8" s="1">
-        <v>52</v>
+        <v>191</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1127,41 +1126,41 @@
         <v>51</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C9" s="8"/>
-      <c r="D9" s="17" t="s">
-        <v>62</v>
+      <c r="D9" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="E9">
-        <v>10.7814918</v>
+        <v>10.8644079</v>
       </c>
       <c r="F9">
-        <v>106.7028325</v>
+        <v>106.7455702</v>
       </c>
       <c r="G9" s="1">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
-        <v>61</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>133</v>
+        <v>51</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>135</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10">
-        <v>10.910496800000001</v>
-      </c>
-      <c r="F10">
-        <v>106.7720695</v>
+      <c r="E10" s="1">
+        <v>10.797376</v>
+      </c>
+      <c r="F10" s="1">
+        <v>106.6599927</v>
       </c>
       <c r="G10" s="1">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1170,71 +1169,67 @@
       <c r="A11" s="7">
         <v>51</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="B11" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
       <c r="E11">
-        <v>10.754680199999999</v>
+        <v>10.752404</v>
       </c>
       <c r="F11">
-        <v>106.6586923</v>
+        <v>106.68212269999999</v>
       </c>
       <c r="G11" s="1">
-        <v>86</v>
+        <v>301</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>72</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>143</v>
+      <c r="A12" s="7">
+        <v>51</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>108</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>83</v>
+        <v>35</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="E12">
-        <v>11.1496355</v>
+        <v>10.7744357</v>
       </c>
       <c r="F12">
-        <v>106.8429288</v>
+        <v>106.6838133</v>
       </c>
       <c r="G12" s="1">
-        <v>87</v>
+        <v>380</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18">
-        <v>61</v>
+      <c r="A13" s="7">
+        <v>51</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>73</v>
+        <v>113</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="E13">
-        <v>11.1639348</v>
+        <v>10.769371</v>
       </c>
       <c r="F13">
-        <v>106.59009639999999</v>
+        <v>106.67093300000001</v>
       </c>
       <c r="G13" s="1">
-        <v>131</v>
+        <v>857</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1244,41 +1239,45 @@
         <v>51</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="5" t="s">
-        <v>57</v>
+        <v>114</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="E14">
-        <v>10.591458100000001</v>
+        <v>11.034454</v>
       </c>
       <c r="F14">
-        <v>106.8149227</v>
+        <v>106.5230191</v>
       </c>
       <c r="G14" s="1">
-        <v>139</v>
+        <v>995</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15">
-        <v>10.975711</v>
-      </c>
-      <c r="F15">
-        <v>106.501437</v>
+        <v>93</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10.59721</v>
+      </c>
+      <c r="F15" s="1">
+        <v>106.9759614</v>
       </c>
       <c r="G15" s="1">
-        <v>147</v>
+        <v>999</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1288,43 +1287,47 @@
         <v>51</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="27" t="s">
-        <v>61</v>
+        <v>100</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="E16">
-        <v>10.3924834</v>
+        <v>10.853793400000001</v>
       </c>
       <c r="F16">
-        <v>107.127064</v>
+        <v>106.7532921</v>
       </c>
       <c r="G16" s="1">
-        <v>174</v>
+        <v>1003</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
-        <v>61</v>
+      <c r="A17" s="7">
+        <v>51</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>11.0854347</v>
+        <v>10.763468</v>
       </c>
       <c r="F17">
-        <v>106.77769259999999</v>
+        <v>106.649007</v>
       </c>
       <c r="G17" s="1">
-        <v>191</v>
+        <v>1121</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1334,20 +1337,22 @@
         <v>51</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18">
-        <v>12.060221200000001</v>
-      </c>
-      <c r="F18">
-        <v>107.10738720000001</v>
+        <v>103</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10.833179100000001</v>
+      </c>
+      <c r="F18" s="1">
+        <v>106.7754443</v>
       </c>
       <c r="G18" s="1">
-        <v>191</v>
+        <v>1175</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1357,20 +1362,22 @@
         <v>51</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="10" t="s">
-        <v>41</v>
+        <v>101</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="E19">
-        <v>10.8644079</v>
+        <v>10.8424069</v>
       </c>
       <c r="F19">
-        <v>106.7455702</v>
+        <v>106.82139119999999</v>
       </c>
       <c r="G19" s="1">
-        <v>198</v>
+        <v>1243</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1379,69 +1386,73 @@
       <c r="A20" s="7">
         <v>51</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="1">
-        <v>10.797376</v>
-      </c>
-      <c r="F20" s="1">
-        <v>106.6599927</v>
+      <c r="B20" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>10.8689663</v>
+      </c>
+      <c r="F20">
+        <v>106.6001974</v>
       </c>
       <c r="G20" s="1">
-        <v>267</v>
+        <v>1253</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>72</v>
+      <c r="A21" s="7">
+        <v>51</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>81</v>
+        <v>17</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>10.6913866</v>
+        <v>10.754125999999999</v>
       </c>
       <c r="F21">
-        <v>106.5862588</v>
+        <v>106.63513</v>
       </c>
       <c r="G21" s="1">
-        <v>295</v>
+        <v>1285</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>72</v>
+      <c r="A22" s="7">
+        <v>51</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>78</v>
+        <v>26</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="E22">
-        <v>10.756917</v>
+        <v>10.804119999999999</v>
       </c>
       <c r="F22">
-        <v>106.7180599</v>
+        <v>106.710095</v>
       </c>
       <c r="G22" s="1">
-        <v>299</v>
+        <v>1332</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1450,19 +1461,23 @@
       <c r="A23" s="7">
         <v>51</v>
       </c>
-      <c r="B23" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="E23">
-        <v>10.752404</v>
+        <v>10.7279537</v>
       </c>
       <c r="F23">
-        <v>106.68212269999999</v>
+        <v>106.6074327</v>
       </c>
       <c r="G23" s="1">
-        <v>301</v>
+        <v>1369</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1472,143 +1487,141 @@
         <v>51</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>10.7744357</v>
+        <v>10.4068769</v>
       </c>
       <c r="F24">
-        <v>106.6838133</v>
+        <v>106.9418831</v>
       </c>
       <c r="G24" s="1">
-        <v>380</v>
+        <v>1440</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>72</v>
+      <c r="A25" s="7">
+        <v>51</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25">
-        <v>11.2894361</v>
-      </c>
-      <c r="F25">
-        <v>106.7949788</v>
+        <v>18</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="1">
+        <v>11.242782200000001</v>
+      </c>
+      <c r="F25" s="1">
+        <v>106.73288789999999</v>
       </c>
       <c r="G25" s="1">
-        <v>534</v>
+        <v>1458</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>72</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>80</v>
-      </c>
+      <c r="A26" s="7">
+        <v>51</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
       <c r="E26">
-        <v>11.2879635</v>
+        <v>10.854276799999999</v>
       </c>
       <c r="F26">
-        <v>106.3913776</v>
+        <v>106.7512353</v>
       </c>
       <c r="G26" s="1">
-        <v>625</v>
+        <v>1503</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18">
-        <v>61</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>66</v>
+      <c r="A27" s="7">
+        <v>51</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="E27">
-        <v>10.791648</v>
+        <v>10.99512</v>
       </c>
       <c r="F27">
-        <v>106.6697379</v>
+        <v>106.65606699999999</v>
       </c>
       <c r="G27" s="1">
-        <v>705</v>
+        <v>1503</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>72</v>
+      <c r="A28" s="7">
+        <v>51</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28">
-        <v>10.9781475</v>
-      </c>
-      <c r="F28">
-        <v>106.65141079999999</v>
+        <v>34</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8.6884721000000003</v>
+      </c>
+      <c r="F28" s="1">
+        <v>106.5955307</v>
       </c>
       <c r="G28" s="1">
-        <v>786</v>
+        <v>1656</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="18">
-        <v>61</v>
+      <c r="A29" s="7">
+        <v>51</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3" t="s">
-        <v>71</v>
+        <v>117</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="E29">
-        <v>10.792902099999999</v>
+        <v>10.7967716</v>
       </c>
       <c r="F29">
-        <v>106.62057110000001</v>
+        <v>106.6627697</v>
       </c>
       <c r="G29" s="1">
-        <v>829</v>
+        <v>1662</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1618,66 +1631,72 @@
         <v>51</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="10" t="s">
-        <v>40</v>
+        <v>88</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>10.769371</v>
+        <v>10.6798705</v>
       </c>
       <c r="F30">
-        <v>106.67093300000001</v>
+        <v>106.7478354</v>
       </c>
       <c r="G30" s="1">
-        <v>857</v>
+        <v>1840</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18">
-        <v>61</v>
+      <c r="A31" s="7">
+        <v>51</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31">
-        <v>10.7805435</v>
-      </c>
-      <c r="F31">
-        <v>106.6715413</v>
+        <v>104</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="1">
+        <v>11.4531648</v>
+      </c>
+      <c r="F31" s="1">
+        <v>106.7753458</v>
       </c>
       <c r="G31" s="1">
-        <v>877</v>
+        <v>1841</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="18">
-        <v>61</v>
+      <c r="A32" s="7">
+        <v>51</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="1" t="s">
-        <v>67</v>
+        <v>106</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>10.7747016</v>
+        <v>10.781197199999999</v>
       </c>
       <c r="F32">
-        <v>106.64813220000001</v>
+        <v>106.75778560000001</v>
       </c>
       <c r="G32" s="1">
-        <v>959</v>
+        <v>1943</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1687,20 +1706,22 @@
         <v>51</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9" t="s">
-        <v>42</v>
+        <v>95</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>11.034454</v>
+        <v>10.367577300000001</v>
       </c>
       <c r="F33">
-        <v>106.5230191</v>
+        <v>107.07491640000001</v>
       </c>
       <c r="G33" s="1">
-        <v>995</v>
+        <v>2038</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1710,22 +1731,22 @@
         <v>51</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="1">
-        <v>10.59721</v>
-      </c>
-      <c r="F34" s="1">
-        <v>106.9759614</v>
+        <v>58</v>
+      </c>
+      <c r="E34">
+        <v>10.509597100000001</v>
+      </c>
+      <c r="F34">
+        <v>107.19429890000001</v>
       </c>
       <c r="G34" s="1">
-        <v>999</v>
+        <v>2326</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1735,45 +1756,47 @@
         <v>51</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35">
-        <v>10.853793400000001</v>
-      </c>
-      <c r="F35">
-        <v>106.7532921</v>
+        <v>55</v>
+      </c>
+      <c r="E35" s="1">
+        <v>10.767180400000001</v>
+      </c>
+      <c r="F35" s="1">
+        <v>106.6643491</v>
       </c>
       <c r="G35" s="1">
-        <v>1003</v>
+        <v>2345</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="18">
-        <v>61</v>
+      <c r="A36" s="7">
+        <v>51</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36">
-        <v>10.7903652</v>
-      </c>
-      <c r="F36">
-        <v>106.69001780000001</v>
+        <v>92</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="1">
+        <v>10.7457928</v>
+      </c>
+      <c r="F36" s="1">
+        <v>106.66039960000001</v>
       </c>
       <c r="G36" s="1">
-        <v>1100</v>
+        <v>2441</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1783,22 +1806,22 @@
         <v>51</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37">
-        <v>10.763468</v>
-      </c>
-      <c r="F37">
-        <v>106.649007</v>
+        <v>51</v>
+      </c>
+      <c r="E37" s="1">
+        <v>10.597046799999999</v>
+      </c>
+      <c r="F37" s="1">
+        <v>107.05596540000001</v>
       </c>
       <c r="G37" s="1">
-        <v>1121</v>
+        <v>2806</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1808,22 +1831,22 @@
         <v>51</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>4</v>
       </c>
       <c r="E38" s="1">
-        <v>10.833179100000001</v>
+        <v>10.8675332</v>
       </c>
       <c r="F38" s="1">
-        <v>106.7754443</v>
+        <v>106.63021790000001</v>
       </c>
       <c r="G38" s="1">
-        <v>1175</v>
+        <v>2877</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1833,22 +1856,22 @@
         <v>51</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E39">
-        <v>10.8424069</v>
+        <v>10.9083784</v>
       </c>
       <c r="F39">
-        <v>106.82139119999999</v>
+        <v>106.6923918</v>
       </c>
       <c r="G39" s="1">
-        <v>1243</v>
+        <v>2930</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1858,22 +1881,22 @@
         <v>51</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40">
-        <v>10.8689663</v>
-      </c>
-      <c r="F40">
-        <v>106.6001974</v>
+        <v>52</v>
+      </c>
+      <c r="E40" s="1">
+        <v>10.5388123</v>
+      </c>
+      <c r="F40" s="1">
+        <v>107.4099504</v>
       </c>
       <c r="G40" s="1">
-        <v>1253</v>
+        <v>2979</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1883,22 +1906,22 @@
         <v>51</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>17</v>
+        <v>112</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E41">
-        <v>10.754125999999999</v>
+        <v>10.7531734</v>
       </c>
       <c r="F41">
-        <v>106.63513</v>
+        <v>106.6784356</v>
       </c>
       <c r="G41" s="1">
-        <v>1285</v>
+        <v>2999</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1908,514 +1931,488 @@
         <v>61</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E42">
-        <v>10.9032637</v>
+        <v>10.737691399999999</v>
       </c>
       <c r="F42">
-        <v>106.7062672</v>
+        <v>106.726889</v>
       </c>
       <c r="G42" s="1">
-        <v>1293</v>
+        <v>36</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
-        <v>51</v>
+      <c r="A43" s="18">
+        <v>61</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>49</v>
+        <v>132</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="E43">
-        <v>10.804119999999999</v>
+        <v>10.756396000000001</v>
       </c>
       <c r="F43">
-        <v>106.710095</v>
+        <v>106.682446</v>
       </c>
       <c r="G43" s="1">
-        <v>1332</v>
+        <v>38</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4"/>
       <c r="E44">
-        <v>10.7279537</v>
+        <v>10.843193400000001</v>
       </c>
       <c r="F44">
-        <v>106.6074327</v>
+        <v>106.67462020000001</v>
       </c>
       <c r="G44" s="1">
-        <v>1369</v>
+        <v>44</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
-        <v>51</v>
+      <c r="A45" s="18">
+        <v>61</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>2</v>
+        <v>130</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="E45">
-        <v>10.4068769</v>
+        <v>10.879506900000001</v>
       </c>
       <c r="F45">
-        <v>106.9418831</v>
+        <v>106.6779872</v>
       </c>
       <c r="G45" s="1">
-        <v>1440</v>
+        <v>52</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="1">
-        <v>11.242782200000001</v>
-      </c>
-      <c r="F46" s="1">
-        <v>106.73288789999999</v>
+        <v>133</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="31"/>
+      <c r="E46">
+        <v>10.910496800000001</v>
+      </c>
+      <c r="F46">
+        <v>106.7720695</v>
       </c>
       <c r="G46" s="1">
-        <v>1458</v>
+        <v>78</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
-        <v>51</v>
-      </c>
-      <c r="B47" s="29" t="s">
-        <v>118</v>
+      <c r="A47" s="18">
+        <v>61</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>129</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="E47">
-        <v>10.854276799999999</v>
+        <v>11.1639348</v>
       </c>
       <c r="F47">
-        <v>106.7512353</v>
+        <v>106.59009639999999</v>
       </c>
       <c r="G47" s="1">
-        <v>1503</v>
+        <v>131</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
-        <v>51</v>
+      <c r="A48" s="18">
+        <v>61</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>11</v>
+        <v>128</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="E48">
-        <v>10.99512</v>
+        <v>11.0854347</v>
       </c>
       <c r="F48">
-        <v>106.65606699999999</v>
+        <v>106.77769259999999</v>
       </c>
       <c r="G48" s="1">
-        <v>1503</v>
+        <v>191</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="7">
-        <v>51</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="1">
-        <v>8.6884721000000003</v>
-      </c>
-      <c r="F49" s="1">
-        <v>106.5955307</v>
+      <c r="A49" s="18">
+        <v>61</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49">
+        <v>10.791648</v>
+      </c>
+      <c r="F49">
+        <v>106.6697379</v>
       </c>
       <c r="G49" s="1">
-        <v>1656</v>
+        <v>705</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
-        <v>51</v>
+      <c r="A50" s="18">
+        <v>61</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="34" t="s">
-        <v>63</v>
+        <v>125</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="33" t="s">
+        <v>71</v>
       </c>
       <c r="E50">
-        <v>10.7967716</v>
+        <v>10.792902099999999</v>
       </c>
       <c r="F50">
-        <v>106.6627697</v>
+        <v>106.62057110000001</v>
       </c>
       <c r="G50" s="1">
-        <v>1662</v>
+        <v>829</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7">
-        <v>51</v>
+      <c r="A51" s="18">
+        <v>61</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>5</v>
+        <v>123</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="E51">
-        <v>10.6798705</v>
+        <v>10.7805435</v>
       </c>
       <c r="F51">
-        <v>106.7478354</v>
+        <v>106.6715413</v>
       </c>
       <c r="G51" s="1">
-        <v>1840</v>
+        <v>877</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7">
-        <v>51</v>
+      <c r="A52" s="18">
+        <v>61</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="1">
-        <v>11.4531648</v>
-      </c>
-      <c r="F52" s="1">
-        <v>106.7753458</v>
+        <v>126</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52">
+        <v>10.7747016</v>
+      </c>
+      <c r="F52">
+        <v>106.64813220000001</v>
       </c>
       <c r="G52" s="1">
-        <v>1841</v>
+        <v>959</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
-        <v>51</v>
+      <c r="A53" s="18">
+        <v>61</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>9</v>
+        <v>127</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="E53">
-        <v>10.781197199999999</v>
+        <v>10.7903652</v>
       </c>
       <c r="F53">
-        <v>106.75778560000001</v>
+        <v>106.69001780000001</v>
       </c>
       <c r="G53" s="1">
-        <v>1943</v>
+        <v>1100</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
-        <v>51</v>
+      <c r="A54" s="18">
+        <v>61</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>8</v>
+        <v>124</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="E54">
-        <v>10.367577300000001</v>
+        <v>10.9032637</v>
       </c>
       <c r="F54">
-        <v>107.07491640000001</v>
+        <v>106.7062672</v>
       </c>
       <c r="G54" s="1">
-        <v>2038</v>
+        <v>1293</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="7">
-        <v>51</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>146</v>
+      <c r="A55" s="3">
+        <v>72</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>58</v>
+        <v>17</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E55">
-        <v>10.509597100000001</v>
+        <v>11.2583871</v>
       </c>
       <c r="F55">
-        <v>107.19429890000001</v>
+        <v>106.60756689999999</v>
       </c>
       <c r="G55" s="1">
-        <v>2326</v>
+        <v>17</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7">
-        <v>51</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>96</v>
+      <c r="A56" s="3">
+        <v>72</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E56" s="1">
-        <v>10.767180400000001</v>
-      </c>
-      <c r="F56" s="1">
-        <v>106.6643491</v>
+        <v>18</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E56">
+        <v>11.1496355</v>
+      </c>
+      <c r="F56">
+        <v>106.8429288</v>
       </c>
       <c r="G56" s="1">
-        <v>2345</v>
+        <v>87</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="1">
-        <v>10.7457928</v>
-      </c>
-      <c r="F57" s="1">
-        <v>106.66039960000001</v>
+        <v>141</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="4"/>
+      <c r="E57">
+        <v>10.975711</v>
+      </c>
+      <c r="F57">
+        <v>106.501437</v>
       </c>
       <c r="G57" s="1">
-        <v>2441</v>
+        <v>147</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7">
-        <v>51</v>
+      <c r="A58" s="3">
+        <v>72</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E58" s="1">
-        <v>10.597046799999999</v>
-      </c>
-      <c r="F58" s="1">
-        <v>107.05596540000001</v>
+        <v>15</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58">
+        <v>10.6913866</v>
+      </c>
+      <c r="F58">
+        <v>106.5862588</v>
       </c>
       <c r="G58" s="1">
-        <v>2806</v>
+        <v>295</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="7">
-        <v>51</v>
+      <c r="A59" s="3">
+        <v>72</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="1">
-        <v>10.8675332</v>
-      </c>
-      <c r="F59" s="1">
-        <v>106.63021790000001</v>
+        <v>14</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59">
+        <v>10.756917</v>
+      </c>
+      <c r="F59">
+        <v>106.7180599</v>
       </c>
       <c r="G59" s="1">
-        <v>2877</v>
+        <v>299</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="7">
-        <v>51</v>
+      <c r="A60" s="3">
+        <v>72</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>46</v>
+        <v>13</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>79</v>
       </c>
       <c r="E60">
-        <v>10.9083784</v>
+        <v>11.2894361</v>
       </c>
       <c r="F60">
-        <v>106.6923918</v>
+        <v>106.7949788</v>
       </c>
       <c r="G60" s="1">
-        <v>2930</v>
+        <v>534</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="7">
-        <v>51</v>
+      <c r="A61" s="3">
+        <v>72</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E61" s="1">
-        <v>10.5388123</v>
-      </c>
-      <c r="F61" s="1">
-        <v>107.4099504</v>
+        <v>14</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61">
+        <v>11.2879635</v>
+      </c>
+      <c r="F61">
+        <v>106.3913776</v>
       </c>
       <c r="G61" s="1">
-        <v>2979</v>
+        <v>625</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="7">
-        <v>51</v>
+      <c r="A62" s="3">
+        <v>72</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>59</v>
+        <v>136</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>77</v>
       </c>
       <c r="E62">
-        <v>10.7531734</v>
+        <v>10.9781475</v>
       </c>
       <c r="F62">
-        <v>106.6784356</v>
+        <v>106.65141079999999</v>
       </c>
       <c r="G62" s="1">
-        <v>2999</v>
+        <v>786</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -12499,7 +12496,7 @@
   </sheetData>
   <autoFilter ref="A1:G62" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">
-      <sortCondition ref="G1:G62"/>
+      <sortCondition ref="A1:A62"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">

--- a/dieu tri.xlsx
+++ b/dieu tri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive - MSFT\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C125666-A928-4F94-AE34-956F7B6DA343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C3EBF5-4FD9-45E2-92BC-B9D9B363AADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -615,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -698,16 +698,20 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -984,22 +988,26 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
-        <v>51</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="A3" s="3">
+        <v>72</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>82</v>
+      </c>
       <c r="E3">
-        <v>10.779844499999999</v>
+        <v>11.2583871</v>
       </c>
       <c r="F3">
-        <v>106.68180719999999</v>
+        <v>106.60756689999999</v>
       </c>
       <c r="G3" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1008,115 +1016,109 @@
       <c r="A4" s="7">
         <v>51</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="B4" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
       <c r="E4">
-        <v>10.7814918</v>
+        <v>10.779844499999999</v>
       </c>
       <c r="F4">
-        <v>106.7028325</v>
+        <v>106.68180719999999</v>
       </c>
       <c r="G4" s="1">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>51</v>
+      <c r="A5" s="18">
+        <v>61</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
+        <v>131</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>10.754680199999999</v>
+        <v>10.737691399999999</v>
       </c>
       <c r="F5">
-        <v>106.6586923</v>
+        <v>106.726889</v>
       </c>
       <c r="G5" s="1">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>51</v>
+      <c r="A6" s="18">
+        <v>61</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5" t="s">
-        <v>57</v>
+        <v>132</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="E6">
-        <v>10.591458100000001</v>
+        <v>10.756396000000001</v>
       </c>
       <c r="F6">
-        <v>106.8149227</v>
+        <v>106.682446</v>
       </c>
       <c r="G6" s="1">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="27" t="s">
-        <v>61</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
       <c r="E7">
-        <v>10.3924834</v>
+        <v>10.843193400000001</v>
       </c>
       <c r="F7">
-        <v>107.127064</v>
+        <v>106.67462020000001</v>
       </c>
       <c r="G7" s="1">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>51</v>
+      <c r="A8" s="18">
+        <v>61</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="16" t="s">
-        <v>60</v>
+        <v>130</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="E8">
-        <v>12.060221200000001</v>
+        <v>10.879506900000001</v>
       </c>
       <c r="F8">
-        <v>107.10738720000001</v>
+        <v>106.6779872</v>
       </c>
       <c r="G8" s="1">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1126,41 +1128,41 @@
         <v>51</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C9" s="8"/>
-      <c r="D9" s="10" t="s">
-        <v>41</v>
+      <c r="D9" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="E9">
-        <v>10.8644079</v>
+        <v>10.7814918</v>
       </c>
       <c r="F9">
-        <v>106.7455702</v>
+        <v>106.7028325</v>
       </c>
       <c r="G9" s="1">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
-        <v>51</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>135</v>
+        <v>61</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>133</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="1">
-        <v>10.797376</v>
-      </c>
-      <c r="F10" s="1">
-        <v>106.6599927</v>
+      <c r="E10">
+        <v>10.910496800000001</v>
+      </c>
+      <c r="F10">
+        <v>106.7720695</v>
       </c>
       <c r="G10" s="1">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1169,67 +1171,71 @@
       <c r="A11" s="7">
         <v>51</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
+      <c r="B11" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="E11">
-        <v>10.752404</v>
+        <v>10.754680199999999</v>
       </c>
       <c r="F11">
-        <v>106.68212269999999</v>
+        <v>106.6586923</v>
       </c>
       <c r="G11" s="1">
-        <v>301</v>
+        <v>86</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>51</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>108</v>
+      <c r="A12" s="3">
+        <v>72</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>56</v>
+        <v>18</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="E12">
-        <v>10.7744357</v>
+        <v>11.1496355</v>
       </c>
       <c r="F12">
-        <v>106.6838133</v>
+        <v>106.8429288</v>
       </c>
       <c r="G12" s="1">
-        <v>380</v>
+        <v>87</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>51</v>
+      <c r="A13" s="18">
+        <v>61</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="10" t="s">
-        <v>40</v>
+        <v>129</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="E13">
-        <v>10.769371</v>
+        <v>11.1639348</v>
       </c>
       <c r="F13">
-        <v>106.67093300000001</v>
+        <v>106.59009639999999</v>
       </c>
       <c r="G13" s="1">
-        <v>857</v>
+        <v>131</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1239,45 +1245,41 @@
         <v>51</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9" t="s">
-        <v>42</v>
+        <v>109</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="E14">
-        <v>11.034454</v>
+        <v>10.591458100000001</v>
       </c>
       <c r="F14">
-        <v>106.5230191</v>
+        <v>106.8149227</v>
       </c>
       <c r="G14" s="1">
-        <v>995</v>
+        <v>139</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="1">
-        <v>10.59721</v>
-      </c>
-      <c r="F15" s="1">
-        <v>106.9759614</v>
+        <v>141</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15">
+        <v>10.975711</v>
+      </c>
+      <c r="F15">
+        <v>106.501437</v>
       </c>
       <c r="G15" s="1">
-        <v>999</v>
+        <v>147</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1287,22 +1289,20 @@
         <v>51</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>50</v>
+        <v>115</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="E16">
-        <v>10.853793400000001</v>
+        <v>10.3924834</v>
       </c>
       <c r="F16">
-        <v>106.7532921</v>
+        <v>107.127064</v>
       </c>
       <c r="G16" s="1">
-        <v>1003</v>
+        <v>174</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1312,47 +1312,43 @@
         <v>51</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>3</v>
+        <v>110</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="E17">
-        <v>10.763468</v>
+        <v>12.060221200000001</v>
       </c>
       <c r="F17">
-        <v>106.649007</v>
+        <v>107.10738720000001</v>
       </c>
       <c r="G17" s="1">
-        <v>1121</v>
+        <v>191</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
-        <v>51</v>
+      <c r="A18" s="18">
+        <v>61</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="1">
-        <v>10.833179100000001</v>
-      </c>
-      <c r="F18" s="1">
-        <v>106.7754443</v>
+        <v>128</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18">
+        <v>11.0854347</v>
+      </c>
+      <c r="F18">
+        <v>106.77769259999999</v>
       </c>
       <c r="G18" s="1">
-        <v>1175</v>
+        <v>191</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1362,22 +1358,20 @@
         <v>51</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>53</v>
+        <v>111</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="E19">
-        <v>10.8424069</v>
+        <v>10.8644079</v>
       </c>
       <c r="F19">
-        <v>106.82139119999999</v>
+        <v>106.7455702</v>
       </c>
       <c r="G19" s="1">
-        <v>1243</v>
+        <v>198</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1386,73 +1380,69 @@
       <c r="A20" s="7">
         <v>51</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20">
-        <v>10.8689663</v>
-      </c>
-      <c r="F20">
-        <v>106.6001974</v>
+      <c r="B20" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="1">
+        <v>10.797376</v>
+      </c>
+      <c r="F20" s="1">
+        <v>106.6599927</v>
       </c>
       <c r="G20" s="1">
-        <v>1253</v>
+        <v>267</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <v>51</v>
+      <c r="A21" s="3">
+        <v>72</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>43</v>
+        <v>15</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="E21">
-        <v>10.754125999999999</v>
+        <v>10.6913866</v>
       </c>
       <c r="F21">
-        <v>106.63513</v>
+        <v>106.5862588</v>
       </c>
       <c r="G21" s="1">
-        <v>1285</v>
+        <v>295</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
-        <v>51</v>
+      <c r="A22" s="3">
+        <v>72</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>49</v>
+        <v>14</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>78</v>
       </c>
       <c r="E22">
-        <v>10.804119999999999</v>
+        <v>10.756917</v>
       </c>
       <c r="F22">
-        <v>106.710095</v>
+        <v>106.7180599</v>
       </c>
       <c r="G22" s="1">
-        <v>1332</v>
+        <v>299</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1461,23 +1451,19 @@
       <c r="A23" s="7">
         <v>51</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="B23" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4"/>
       <c r="E23">
-        <v>10.7279537</v>
+        <v>10.752404</v>
       </c>
       <c r="F23">
-        <v>106.6074327</v>
+        <v>106.68212269999999</v>
       </c>
       <c r="G23" s="1">
-        <v>1369</v>
+        <v>301</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1487,141 +1473,143 @@
         <v>51</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E24">
-        <v>10.4068769</v>
+        <v>10.7744357</v>
       </c>
       <c r="F24">
-        <v>106.9418831</v>
+        <v>106.6838133</v>
       </c>
       <c r="G24" s="1">
-        <v>1440</v>
+        <v>380</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
-        <v>51</v>
+      <c r="A25" s="3">
+        <v>72</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="1">
-        <v>11.242782200000001</v>
-      </c>
-      <c r="F25" s="1">
-        <v>106.73288789999999</v>
+        <v>13</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25">
+        <v>11.2894361</v>
+      </c>
+      <c r="F25">
+        <v>106.7949788</v>
       </c>
       <c r="G25" s="1">
-        <v>1458</v>
+        <v>534</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
-        <v>51</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
+      <c r="A26" s="3">
+        <v>72</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>80</v>
+      </c>
       <c r="E26">
-        <v>10.854276799999999</v>
+        <v>11.2879635</v>
       </c>
       <c r="F26">
-        <v>106.7512353</v>
+        <v>106.3913776</v>
       </c>
       <c r="G26" s="1">
-        <v>1503</v>
+        <v>625</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
-        <v>51</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>11</v>
+      <c r="A27" s="18">
+        <v>61</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="E27">
-        <v>10.99512</v>
+        <v>10.791648</v>
       </c>
       <c r="F27">
-        <v>106.65606699999999</v>
+        <v>106.6697379</v>
       </c>
       <c r="G27" s="1">
-        <v>1503</v>
+        <v>705</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
-        <v>51</v>
+      <c r="A28" s="3">
+        <v>72</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="1">
-        <v>8.6884721000000003</v>
-      </c>
-      <c r="F28" s="1">
-        <v>106.5955307</v>
+        <v>13</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28">
+        <v>10.9781475</v>
+      </c>
+      <c r="F28">
+        <v>106.65141079999999</v>
       </c>
       <c r="G28" s="1">
-        <v>1656</v>
+        <v>786</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
-        <v>51</v>
+      <c r="A29" s="18">
+        <v>61</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="16" t="s">
-        <v>63</v>
+        <v>125</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="E29">
-        <v>10.7967716</v>
+        <v>10.792902099999999</v>
       </c>
       <c r="F29">
-        <v>106.6627697</v>
+        <v>106.62057110000001</v>
       </c>
       <c r="G29" s="1">
-        <v>1662</v>
+        <v>829</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1631,72 +1619,66 @@
         <v>51</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>5</v>
+        <v>113</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="E30">
-        <v>10.6798705</v>
+        <v>10.769371</v>
       </c>
       <c r="F30">
-        <v>106.7478354</v>
+        <v>106.67093300000001</v>
       </c>
       <c r="G30" s="1">
-        <v>1840</v>
+        <v>857</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
-        <v>51</v>
+      <c r="A31" s="18">
+        <v>61</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="1">
-        <v>11.4531648</v>
-      </c>
-      <c r="F31" s="1">
-        <v>106.7753458</v>
+        <v>123</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31">
+        <v>10.7805435</v>
+      </c>
+      <c r="F31">
+        <v>106.6715413</v>
       </c>
       <c r="G31" s="1">
-        <v>1841</v>
+        <v>877</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
-        <v>51</v>
+      <c r="A32" s="18">
+        <v>61</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>9</v>
+        <v>126</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="33" t="s">
+        <v>67</v>
       </c>
       <c r="E32">
-        <v>10.781197199999999</v>
+        <v>10.7747016</v>
       </c>
       <c r="F32">
-        <v>106.75778560000001</v>
+        <v>106.64813220000001</v>
       </c>
       <c r="G32" s="1">
-        <v>1943</v>
+        <v>959</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1706,22 +1688,20 @@
         <v>51</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>8</v>
+        <v>114</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="E33">
-        <v>10.367577300000001</v>
+        <v>11.034454</v>
       </c>
       <c r="F33">
-        <v>107.07491640000001</v>
+        <v>106.5230191</v>
       </c>
       <c r="G33" s="1">
-        <v>2038</v>
+        <v>995</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1731,22 +1711,22 @@
         <v>51</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34">
-        <v>10.509597100000001</v>
-      </c>
-      <c r="F34">
-        <v>107.19429890000001</v>
+        <v>47</v>
+      </c>
+      <c r="E34" s="1">
+        <v>10.59721</v>
+      </c>
+      <c r="F34" s="1">
+        <v>106.9759614</v>
       </c>
       <c r="G34" s="1">
-        <v>2326</v>
+        <v>999</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1756,47 +1736,45 @@
         <v>51</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="1">
-        <v>10.767180400000001</v>
-      </c>
-      <c r="F35" s="1">
-        <v>106.6643491</v>
+        <v>50</v>
+      </c>
+      <c r="E35">
+        <v>10.853793400000001</v>
+      </c>
+      <c r="F35">
+        <v>106.7532921</v>
       </c>
       <c r="G35" s="1">
-        <v>2345</v>
+        <v>1003</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
-        <v>51</v>
+      <c r="A36" s="18">
+        <v>61</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="1">
-        <v>10.7457928</v>
-      </c>
-      <c r="F36" s="1">
-        <v>106.66039960000001</v>
+        <v>127</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36">
+        <v>10.7903652</v>
+      </c>
+      <c r="F36">
+        <v>106.69001780000001</v>
       </c>
       <c r="G36" s="1">
-        <v>2441</v>
+        <v>1100</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1806,22 +1784,22 @@
         <v>51</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="1">
-        <v>10.597046799999999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>107.05596540000001</v>
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>10.763468</v>
+      </c>
+      <c r="F37">
+        <v>106.649007</v>
       </c>
       <c r="G37" s="1">
-        <v>2806</v>
+        <v>1121</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1831,22 +1809,22 @@
         <v>51</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>45</v>
       </c>
       <c r="E38" s="1">
-        <v>10.8675332</v>
+        <v>10.833179100000001</v>
       </c>
       <c r="F38" s="1">
-        <v>106.63021790000001</v>
+        <v>106.7754443</v>
       </c>
       <c r="G38" s="1">
-        <v>2877</v>
+        <v>1175</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1856,22 +1834,22 @@
         <v>51</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E39">
-        <v>10.9083784</v>
+        <v>10.8424069</v>
       </c>
       <c r="F39">
-        <v>106.6923918</v>
+        <v>106.82139119999999</v>
       </c>
       <c r="G39" s="1">
-        <v>2930</v>
+        <v>1243</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1881,22 +1859,22 @@
         <v>51</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="1">
-        <v>10.5388123</v>
-      </c>
-      <c r="F40" s="1">
-        <v>107.4099504</v>
+        <v>6</v>
+      </c>
+      <c r="E40">
+        <v>10.8689663</v>
+      </c>
+      <c r="F40">
+        <v>106.6001974</v>
       </c>
       <c r="G40" s="1">
-        <v>2979</v>
+        <v>1253</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1906,22 +1884,22 @@
         <v>51</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>36</v>
+        <v>89</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E41">
-        <v>10.7531734</v>
+        <v>10.754125999999999</v>
       </c>
       <c r="F41">
-        <v>106.6784356</v>
+        <v>106.63513</v>
       </c>
       <c r="G41" s="1">
-        <v>2999</v>
+        <v>1285</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1931,488 +1909,514 @@
         <v>61</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E42">
-        <v>10.737691399999999</v>
+        <v>10.9032637</v>
       </c>
       <c r="F42">
-        <v>106.726889</v>
+        <v>106.7062672</v>
       </c>
       <c r="G42" s="1">
-        <v>36</v>
+        <v>1293</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="18">
-        <v>61</v>
+      <c r="A43" s="7">
+        <v>51</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3" t="s">
-        <v>76</v>
+        <v>98</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="E43">
-        <v>10.756396000000001</v>
+        <v>10.804119999999999</v>
       </c>
       <c r="F43">
-        <v>106.682446</v>
+        <v>106.710095</v>
       </c>
       <c r="G43" s="1">
-        <v>38</v>
+        <v>1332</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="E44">
-        <v>10.843193400000001</v>
+        <v>10.7279537</v>
       </c>
       <c r="F44">
-        <v>106.67462020000001</v>
+        <v>106.6074327</v>
       </c>
       <c r="G44" s="1">
-        <v>44</v>
+        <v>1369</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="18">
-        <v>61</v>
+      <c r="A45" s="7">
+        <v>51</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3" t="s">
-        <v>74</v>
+        <v>87</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>10.879506900000001</v>
+        <v>10.4068769</v>
       </c>
       <c r="F45">
-        <v>106.6779872</v>
+        <v>106.9418831</v>
       </c>
       <c r="G45" s="1">
-        <v>52</v>
+        <v>1440</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="31"/>
-      <c r="E46">
-        <v>10.910496800000001</v>
-      </c>
-      <c r="F46">
-        <v>106.7720695</v>
+        <v>90</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="1">
+        <v>11.242782200000001</v>
+      </c>
+      <c r="F46" s="1">
+        <v>106.73288789999999</v>
       </c>
       <c r="G46" s="1">
-        <v>78</v>
+        <v>1458</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="18">
-        <v>61</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>129</v>
+      <c r="A47" s="7">
+        <v>51</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>118</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="3" t="s">
-        <v>73</v>
-      </c>
+      <c r="D47" s="4"/>
       <c r="E47">
-        <v>11.1639348</v>
+        <v>10.854276799999999</v>
       </c>
       <c r="F47">
-        <v>106.59009639999999</v>
+        <v>106.7512353</v>
       </c>
       <c r="G47" s="1">
-        <v>131</v>
+        <v>1503</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="18">
-        <v>61</v>
+      <c r="A48" s="7">
+        <v>51</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3" t="s">
-        <v>72</v>
+        <v>118</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>11.0854347</v>
+        <v>10.99512</v>
       </c>
       <c r="F48">
-        <v>106.77769259999999</v>
+        <v>106.65606699999999</v>
       </c>
       <c r="G48" s="1">
-        <v>191</v>
+        <v>1503</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="18">
-        <v>61</v>
-      </c>
-      <c r="B49" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E49">
-        <v>10.791648</v>
-      </c>
-      <c r="F49">
-        <v>106.6697379</v>
+      <c r="A49" s="7">
+        <v>51</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1">
+        <v>8.6884721000000003</v>
+      </c>
+      <c r="F49" s="1">
+        <v>106.5955307</v>
       </c>
       <c r="G49" s="1">
-        <v>705</v>
+        <v>1656</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="18">
-        <v>61</v>
+      <c r="A50" s="7">
+        <v>51</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="33" t="s">
-        <v>71</v>
+        <v>117</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="35" t="s">
+        <v>63</v>
       </c>
       <c r="E50">
-        <v>10.792902099999999</v>
+        <v>10.7967716</v>
       </c>
       <c r="F50">
-        <v>106.62057110000001</v>
+        <v>106.6627697</v>
       </c>
       <c r="G50" s="1">
-        <v>829</v>
+        <v>1662</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="18">
-        <v>61</v>
+      <c r="A51" s="7">
+        <v>51</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3" t="s">
-        <v>69</v>
+        <v>88</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="E51">
-        <v>10.7805435</v>
+        <v>10.6798705</v>
       </c>
       <c r="F51">
-        <v>106.6715413</v>
+        <v>106.7478354</v>
       </c>
       <c r="G51" s="1">
-        <v>877</v>
+        <v>1840</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="18">
-        <v>61</v>
+      <c r="A52" s="7">
+        <v>51</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52">
-        <v>10.7747016</v>
-      </c>
-      <c r="F52">
-        <v>106.64813220000001</v>
+        <v>104</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="1">
+        <v>11.4531648</v>
+      </c>
+      <c r="F52" s="1">
+        <v>106.7753458</v>
       </c>
       <c r="G52" s="1">
-        <v>959</v>
+        <v>1841</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="18">
-        <v>61</v>
+      <c r="A53" s="7">
+        <v>51</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3" t="s">
-        <v>70</v>
+        <v>106</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="E53">
-        <v>10.7903652</v>
+        <v>10.781197199999999</v>
       </c>
       <c r="F53">
-        <v>106.69001780000001</v>
+        <v>106.75778560000001</v>
       </c>
       <c r="G53" s="1">
-        <v>1100</v>
+        <v>1943</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="18">
-        <v>61</v>
+      <c r="A54" s="7">
+        <v>51</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E54">
-        <v>10.9032637</v>
+        <v>10.367577300000001</v>
       </c>
       <c r="F54">
-        <v>106.7062672</v>
+        <v>107.07491640000001</v>
       </c>
       <c r="G54" s="1">
-        <v>1293</v>
+        <v>2038</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
-        <v>72</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>142</v>
+      <c r="A55" s="7">
+        <v>51</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" s="28" t="s">
-        <v>82</v>
+        <v>37</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="E55">
-        <v>11.2583871</v>
+        <v>10.509597100000001</v>
       </c>
       <c r="F55">
-        <v>106.60756689999999</v>
+        <v>107.19429890000001</v>
       </c>
       <c r="G55" s="1">
-        <v>17</v>
+        <v>2326</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3">
-        <v>72</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>143</v>
+      <c r="A56" s="7">
+        <v>51</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>96</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E56">
-        <v>11.1496355</v>
-      </c>
-      <c r="F56">
-        <v>106.8429288</v>
+        <v>33</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" s="1">
+        <v>10.767180400000001</v>
+      </c>
+      <c r="F56" s="1">
+        <v>106.6643491</v>
       </c>
       <c r="G56" s="1">
-        <v>87</v>
+        <v>2345</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="4"/>
-      <c r="E57">
-        <v>10.975711</v>
-      </c>
-      <c r="F57">
-        <v>106.501437</v>
+        <v>92</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="1">
+        <v>10.7457928</v>
+      </c>
+      <c r="F57" s="1">
+        <v>106.66039960000001</v>
       </c>
       <c r="G57" s="1">
-        <v>147</v>
+        <v>2441</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3">
-        <v>72</v>
+      <c r="A58" s="7">
+        <v>51</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58">
-        <v>10.6913866</v>
-      </c>
-      <c r="F58">
-        <v>106.5862588</v>
+        <v>28</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="1">
+        <v>10.597046799999999</v>
+      </c>
+      <c r="F58" s="1">
+        <v>107.05596540000001</v>
       </c>
       <c r="G58" s="1">
-        <v>295</v>
+        <v>2806</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3">
-        <v>72</v>
+      <c r="A59" s="7">
+        <v>51</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E59">
-        <v>10.756917</v>
-      </c>
-      <c r="F59">
-        <v>106.7180599</v>
+        <v>15</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1">
+        <v>10.8675332</v>
+      </c>
+      <c r="F59" s="1">
+        <v>106.63021790000001</v>
       </c>
       <c r="G59" s="1">
-        <v>299</v>
+        <v>2877</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="3">
-        <v>72</v>
+      <c r="A60" s="7">
+        <v>51</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="29" t="s">
-        <v>79</v>
+        <v>23</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="E60">
-        <v>11.2894361</v>
+        <v>10.9083784</v>
       </c>
       <c r="F60">
-        <v>106.7949788</v>
+        <v>106.6923918</v>
       </c>
       <c r="G60" s="1">
-        <v>534</v>
+        <v>2930</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
-        <v>72</v>
+      <c r="A61" s="7">
+        <v>51</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E61">
-        <v>11.2879635</v>
-      </c>
-      <c r="F61">
-        <v>106.3913776</v>
+        <v>30</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E61" s="1">
+        <v>10.5388123</v>
+      </c>
+      <c r="F61" s="1">
+        <v>107.4099504</v>
       </c>
       <c r="G61" s="1">
-        <v>625</v>
+        <v>2979</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
-        <v>72</v>
+      <c r="A62" s="7">
+        <v>51</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="26" t="s">
-        <v>77</v>
+        <v>112</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="E62">
-        <v>10.9781475</v>
+        <v>10.7531734</v>
       </c>
       <c r="F62">
-        <v>106.65141079999999</v>
+        <v>106.6784356</v>
       </c>
       <c r="G62" s="1">
-        <v>786</v>
+        <v>2999</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -12496,7 +12500,7 @@
   </sheetData>
   <autoFilter ref="A1:G62" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">
-      <sortCondition ref="A1:A62"/>
+      <sortCondition ref="G1:G62"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">

--- a/dieu tri.xlsx
+++ b/dieu tri.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive - MSFT\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C3EBF5-4FD9-45E2-92BC-B9D9B363AADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB907FC5-6AC6-436F-9418-B1902A0837F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -615,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -685,6 +685,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -692,24 +693,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -969,45 +965,45 @@
         <v>51</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="4" t="s">
-        <v>65</v>
+        <v>109</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="E2">
-        <v>10.8187959</v>
+        <v>10.4068769</v>
       </c>
       <c r="F2">
-        <v>106.6805361</v>
+        <v>106.9418831</v>
       </c>
       <c r="G2" s="1">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>72</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>142</v>
+      <c r="A3" s="7">
+        <v>51</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>108</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>82</v>
+        <v>35</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>11.2583871</v>
+        <v>10.6798705</v>
       </c>
       <c r="F3">
-        <v>106.60756689999999</v>
+        <v>106.7478354</v>
       </c>
       <c r="G3" s="1">
-        <v>17</v>
+        <v>380</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1016,109 +1012,123 @@
       <c r="A4" s="7">
         <v>51</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
+      <c r="B4" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E4">
-        <v>10.779844499999999</v>
+        <v>10.6913866</v>
       </c>
       <c r="F4">
-        <v>106.68180719999999</v>
+        <v>106.5862588</v>
       </c>
       <c r="G4" s="1">
-        <v>21</v>
+        <v>1943</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18">
-        <v>61</v>
+      <c r="A5" s="7">
+        <v>51</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>75</v>
+        <v>98</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="E5">
-        <v>10.737691399999999</v>
+        <v>10.7279537</v>
       </c>
       <c r="F5">
-        <v>106.726889</v>
+        <v>106.6074327</v>
       </c>
       <c r="G5" s="1">
-        <v>36</v>
+        <v>1332</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
-        <v>61</v>
+      <c r="A6" s="7">
+        <v>51</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>76</v>
+        <v>91</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>10.756396000000001</v>
+        <v>10.737691399999999</v>
       </c>
       <c r="F6">
-        <v>106.682446</v>
+        <v>106.726889</v>
       </c>
       <c r="G6" s="1">
-        <v>38</v>
+        <v>1253</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="E7">
-        <v>10.843193400000001</v>
+        <v>10.749357</v>
       </c>
       <c r="F7">
-        <v>106.67462020000001</v>
+        <v>106.683744</v>
       </c>
       <c r="G7" s="1">
-        <v>44</v>
+        <v>2441</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
-        <v>61</v>
+      <c r="A8" s="7">
+        <v>51</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>10.879506900000001</v>
+        <v>10.752404</v>
       </c>
       <c r="F8">
-        <v>106.6779872</v>
+        <v>106.68212269999999</v>
       </c>
       <c r="G8" s="1">
-        <v>52</v>
+        <v>1503</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1128,41 +1138,47 @@
         <v>51</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="s">
-        <v>62</v>
+        <v>146</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="E9">
-        <v>10.7814918</v>
+        <v>10.7531734</v>
       </c>
       <c r="F9">
-        <v>106.7028325</v>
+        <v>106.6784356</v>
       </c>
       <c r="G9" s="1">
-        <v>71</v>
+        <v>2326</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="E10">
-        <v>10.910496800000001</v>
+        <v>10.754125999999999</v>
       </c>
       <c r="F10">
-        <v>106.7720695</v>
+        <v>106.63513</v>
       </c>
       <c r="G10" s="1">
-        <v>78</v>
+        <v>1458</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1172,13 +1188,11 @@
         <v>51</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>64</v>
+        <v>113</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="E11">
         <v>10.754680199999999</v>
@@ -1187,55 +1201,57 @@
         <v>106.6586923</v>
       </c>
       <c r="G11" s="1">
-        <v>86</v>
+        <v>857</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>72</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>143</v>
+      <c r="A12" s="7">
+        <v>51</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>89</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>83</v>
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>11.1496355</v>
+        <v>10.756396000000001</v>
       </c>
       <c r="F12">
-        <v>106.8429288</v>
+        <v>106.682446</v>
       </c>
       <c r="G12" s="1">
-        <v>87</v>
+        <v>1285</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18">
-        <v>61</v>
+      <c r="A13" s="7">
+        <v>51</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>73</v>
+        <v>88</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>11.1639348</v>
+        <v>10.756917</v>
       </c>
       <c r="F13">
-        <v>106.59009639999999</v>
+        <v>106.7180599</v>
       </c>
       <c r="G13" s="1">
-        <v>131</v>
+        <v>1840</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1245,41 +1261,45 @@
         <v>51</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>94</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="D14" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E14">
-        <v>10.591458100000001</v>
+        <v>10.763468</v>
       </c>
       <c r="F14">
-        <v>106.8149227</v>
+        <v>106.649007</v>
       </c>
       <c r="G14" s="1">
-        <v>139</v>
+        <v>2930</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
+        <v>111</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="E15">
-        <v>10.975711</v>
+        <v>10.769371</v>
       </c>
       <c r="F15">
-        <v>106.501437</v>
+        <v>106.67093300000001</v>
       </c>
       <c r="G15" s="1">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1289,20 +1309,22 @@
         <v>51</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="27" t="s">
-        <v>61</v>
+        <v>97</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>10.3924834</v>
+        <v>10.7744357</v>
       </c>
       <c r="F16">
-        <v>107.127064</v>
+        <v>106.6838133</v>
       </c>
       <c r="G16" s="1">
-        <v>174</v>
+        <v>2877</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1312,43 +1334,45 @@
         <v>51</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="16" t="s">
-        <v>60</v>
+        <v>102</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="E17">
-        <v>12.060221200000001</v>
+        <v>10.7747016</v>
       </c>
       <c r="F17">
-        <v>107.10738720000001</v>
+        <v>106.64813220000001</v>
       </c>
       <c r="G17" s="1">
-        <v>191</v>
+        <v>2979</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
-        <v>61</v>
+      <c r="A18" s="7">
+        <v>51</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3" t="s">
-        <v>72</v>
+        <v>117</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="E18">
-        <v>11.0854347</v>
+        <v>10.779844499999999</v>
       </c>
       <c r="F18">
-        <v>106.77769259999999</v>
+        <v>106.68180719999999</v>
       </c>
       <c r="G18" s="1">
-        <v>191</v>
+        <v>1662</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1358,20 +1382,22 @@
         <v>51</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="10" t="s">
-        <v>41</v>
+        <v>95</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>10.8644079</v>
+        <v>10.7805435</v>
       </c>
       <c r="F19">
-        <v>106.7455702</v>
+        <v>106.6715413</v>
       </c>
       <c r="G19" s="1">
-        <v>198</v>
+        <v>2038</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1380,69 +1406,71 @@
       <c r="A20" s="7">
         <v>51</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="1">
-        <v>10.797376</v>
-      </c>
-      <c r="F20" s="1">
-        <v>106.6599927</v>
+      <c r="B20" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>10.781197199999999</v>
+      </c>
+      <c r="F20">
+        <v>106.75778560000001</v>
       </c>
       <c r="G20" s="1">
-        <v>267</v>
+        <v>1121</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>72</v>
+      <c r="A21" s="7">
+        <v>51</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>81</v>
+        <v>110</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="E21">
-        <v>10.6913866</v>
+        <v>10.7814918</v>
       </c>
       <c r="F21">
-        <v>106.5862588</v>
+        <v>106.7028325</v>
       </c>
       <c r="G21" s="1">
-        <v>295</v>
+        <v>191</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>72</v>
+      <c r="A22" s="7">
+        <v>51</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>78</v>
+        <v>13</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>10.756917</v>
+        <v>10.7903652</v>
       </c>
       <c r="F22">
-        <v>106.7180599</v>
+        <v>106.69001780000001</v>
       </c>
       <c r="G22" s="1">
-        <v>299</v>
+        <v>1440</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1451,19 +1479,23 @@
       <c r="A23" s="7">
         <v>51</v>
       </c>
-      <c r="B23" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="E23">
-        <v>10.752404</v>
+        <v>10.791648</v>
       </c>
       <c r="F23">
-        <v>106.68212269999999</v>
+        <v>106.6697379</v>
       </c>
       <c r="G23" s="1">
-        <v>301</v>
+        <v>1003</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1473,143 +1505,143 @@
         <v>51</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E24">
-        <v>10.7744357</v>
+        <v>10.792902099999999</v>
       </c>
       <c r="F24">
-        <v>106.6838133</v>
+        <v>106.62057110000001</v>
       </c>
       <c r="G24" s="1">
-        <v>380</v>
+        <v>1243</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>72</v>
+      <c r="A25" s="7">
+        <v>51</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>79</v>
+        <v>121</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="E25">
-        <v>11.2894361</v>
+        <v>10.7967716</v>
       </c>
       <c r="F25">
-        <v>106.7949788</v>
+        <v>106.6627697</v>
       </c>
       <c r="G25" s="1">
-        <v>534</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>72</v>
+      <c r="A26" s="7">
+        <v>51</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>80</v>
+        <v>33</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="E26">
-        <v>11.2879635</v>
+        <v>10.804119999999999</v>
       </c>
       <c r="F26">
-        <v>106.3913776</v>
+        <v>106.710095</v>
       </c>
       <c r="G26" s="1">
-        <v>625</v>
+        <v>2345</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18">
-        <v>61</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>66</v>
+      <c r="A27" s="7">
+        <v>51</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="E27">
-        <v>10.791648</v>
+        <v>10.8187959</v>
       </c>
       <c r="F27">
-        <v>106.6697379</v>
+        <v>106.6805361</v>
       </c>
       <c r="G27" s="1">
-        <v>705</v>
+        <v>71</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>72</v>
+      <c r="A28" s="7">
+        <v>51</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>77</v>
+        <v>21</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="E28">
-        <v>10.9781475</v>
+        <v>10.8424069</v>
       </c>
       <c r="F28">
-        <v>106.65141079999999</v>
+        <v>106.82139119999999</v>
       </c>
       <c r="G28" s="1">
-        <v>786</v>
+        <v>1175</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="18">
-        <v>61</v>
+      <c r="A29" s="7">
+        <v>51</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3" t="s">
-        <v>71</v>
+        <v>99</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="E29">
-        <v>10.792902099999999</v>
+        <v>10.843193400000001</v>
       </c>
       <c r="F29">
-        <v>106.62057110000001</v>
+        <v>106.67462020000001</v>
       </c>
       <c r="G29" s="1">
-        <v>829</v>
+        <v>2806</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1619,66 +1651,72 @@
         <v>51</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="10" t="s">
-        <v>40</v>
+        <v>104</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="E30">
-        <v>10.769371</v>
+        <v>10.853793400000001</v>
       </c>
       <c r="F30">
-        <v>106.67093300000001</v>
+        <v>106.7532921</v>
       </c>
       <c r="G30" s="1">
-        <v>857</v>
+        <v>1841</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18">
-        <v>61</v>
+      <c r="A31" s="7">
+        <v>51</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3" t="s">
-        <v>69</v>
+        <v>120</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="E31">
-        <v>10.7805435</v>
+        <v>10.854276799999999</v>
       </c>
       <c r="F31">
-        <v>106.6715413</v>
+        <v>106.7512353</v>
       </c>
       <c r="G31" s="1">
-        <v>877</v>
+        <v>86</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="18">
-        <v>61</v>
+      <c r="A32" s="7">
+        <v>51</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="33" t="s">
-        <v>67</v>
+        <v>112</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>59</v>
       </c>
       <c r="E32">
-        <v>10.7747016</v>
+        <v>10.8644079</v>
       </c>
       <c r="F32">
-        <v>106.64813220000001</v>
+        <v>106.7455702</v>
       </c>
       <c r="G32" s="1">
-        <v>959</v>
+        <v>2999</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1688,20 +1726,22 @@
         <v>51</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9" t="s">
-        <v>42</v>
+        <v>107</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>11.034454</v>
+        <v>10.8689663</v>
       </c>
       <c r="F33">
-        <v>106.5230191</v>
+        <v>106.6001974</v>
       </c>
       <c r="G33" s="1">
-        <v>995</v>
+        <v>1656</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1719,11 +1759,11 @@
       <c r="D34" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="1">
-        <v>10.59721</v>
-      </c>
-      <c r="F34" s="1">
-        <v>106.9759614</v>
+      <c r="E34">
+        <v>10.879506900000001</v>
+      </c>
+      <c r="F34">
+        <v>106.6779872</v>
       </c>
       <c r="G34" s="1">
         <v>999</v>
@@ -1735,46 +1775,46 @@
       <c r="A35" s="7">
         <v>51</v>
       </c>
-      <c r="B35" s="25" t="s">
-        <v>100</v>
+      <c r="B35" s="26" t="s">
+        <v>105</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E35">
-        <v>10.853793400000001</v>
+        <v>10.975711</v>
       </c>
       <c r="F35">
-        <v>106.7532921</v>
+        <v>106.501437</v>
       </c>
       <c r="G35" s="1">
-        <v>1003</v>
+        <v>1369</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="18">
+      <c r="A36" s="7">
+        <v>51</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="E36">
-        <v>10.7903652</v>
+        <v>11.034454</v>
       </c>
       <c r="F36">
-        <v>106.69001780000001</v>
+        <v>106.5230191</v>
       </c>
       <c r="G36" s="1">
-        <v>1100</v>
+        <v>174</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1784,122 +1824,112 @@
         <v>51</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>3</v>
+        <v>114</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="E37">
-        <v>10.763468</v>
+        <v>12.060221200000001</v>
       </c>
       <c r="F37">
-        <v>106.649007</v>
+        <v>107.10738720000001</v>
       </c>
       <c r="G37" s="1">
-        <v>1121</v>
+        <v>995</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
-        <v>51</v>
+      <c r="A38" s="18">
+        <v>61</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="1">
-        <v>10.833179100000001</v>
-      </c>
-      <c r="F38" s="1">
-        <v>106.7754443</v>
+        <v>124</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38">
+        <v>10.9032637</v>
+      </c>
+      <c r="F38">
+        <v>106.7062672</v>
       </c>
       <c r="G38" s="1">
-        <v>1175</v>
+        <v>1293</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
-        <v>51</v>
+      <c r="A39" s="18">
+        <v>61</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>53</v>
+        <v>132</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="E39">
-        <v>10.8424069</v>
+        <v>10.9083784</v>
       </c>
       <c r="F39">
-        <v>106.82139119999999</v>
+        <v>106.6923918</v>
       </c>
       <c r="G39" s="1">
-        <v>1243</v>
+        <v>38</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
-        <v>51</v>
+      <c r="A40" s="18">
+        <v>61</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>6</v>
+        <v>123</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="E40">
-        <v>10.8689663</v>
+        <v>10.910496800000001</v>
       </c>
       <c r="F40">
-        <v>106.6001974</v>
+        <v>106.7720695</v>
       </c>
       <c r="G40" s="1">
-        <v>1253</v>
+        <v>877</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="7">
-        <v>51</v>
+      <c r="A41" s="18">
+        <v>61</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>43</v>
+        <v>126</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E41">
-        <v>10.754125999999999</v>
+        <v>10.9781475</v>
       </c>
       <c r="F41">
-        <v>106.63513</v>
+        <v>106.65141079999999</v>
       </c>
       <c r="G41" s="1">
-        <v>1285</v>
+        <v>959</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1908,183 +1938,175 @@
       <c r="A42" s="18">
         <v>61</v>
       </c>
-      <c r="B42" s="25" t="s">
-        <v>124</v>
+      <c r="B42" s="32" t="s">
+        <v>145</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E42">
-        <v>10.9032637</v>
+        <v>10.99512</v>
       </c>
       <c r="F42">
-        <v>106.7062672</v>
+        <v>106.65606699999999</v>
       </c>
       <c r="G42" s="1">
-        <v>1293</v>
+        <v>705</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
-        <v>51</v>
-      </c>
-      <c r="B43" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>49</v>
+      <c r="A43" s="18">
+        <v>61</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="E43">
-        <v>10.804119999999999</v>
+        <v>11.0854347</v>
       </c>
       <c r="F43">
-        <v>106.710095</v>
+        <v>106.77769259999999</v>
       </c>
       <c r="G43" s="1">
-        <v>1332</v>
+        <v>829</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7">
-        <v>51</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>48</v>
+      <c r="A44" s="18">
+        <v>61</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="E44">
-        <v>10.7279537</v>
+        <v>11.1496355</v>
       </c>
       <c r="F44">
-        <v>106.6074327</v>
+        <v>106.8429288</v>
       </c>
       <c r="G44" s="1">
-        <v>1369</v>
+        <v>36</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
-        <v>51</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>2</v>
+      <c r="A45" s="18">
+        <v>61</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="E45">
-        <v>10.4068769</v>
+        <v>11.1639348</v>
       </c>
       <c r="F45">
-        <v>106.9418831</v>
+        <v>106.59009639999999</v>
       </c>
       <c r="G45" s="1">
-        <v>1440</v>
+        <v>1100</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7">
-        <v>51</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="1">
-        <v>11.242782200000001</v>
-      </c>
-      <c r="F46" s="1">
-        <v>106.73288789999999</v>
+      <c r="A46" s="18">
+        <v>61</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46">
+        <v>11.2583871</v>
+      </c>
+      <c r="F46">
+        <v>106.60756689999999</v>
       </c>
       <c r="G46" s="1">
-        <v>1458</v>
+        <v>52</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
-        <v>51</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>118</v>
+      <c r="A47" s="18">
+        <v>61</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="E47">
-        <v>10.854276799999999</v>
+        <v>11.2879635</v>
       </c>
       <c r="F47">
-        <v>106.7512353</v>
+        <v>106.3913776</v>
       </c>
       <c r="G47" s="1">
-        <v>1503</v>
+        <v>191</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
-        <v>51</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>11</v>
+      <c r="A48" s="18">
+        <v>61</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="E48">
-        <v>10.99512</v>
+        <v>11.2894361</v>
       </c>
       <c r="F48">
-        <v>106.65606699999999</v>
+        <v>106.7949788</v>
       </c>
       <c r="G48" s="1">
-        <v>1503</v>
+        <v>131</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="7">
-        <v>51</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>107</v>
+      <c r="A49" s="3">
+        <v>72</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="D49" s="30" t="s">
+        <v>82</v>
       </c>
       <c r="E49" s="1">
         <v>8.6884721000000003</v>
@@ -2093,155 +2115,157 @@
         <v>106.5955307</v>
       </c>
       <c r="G49" s="1">
-        <v>1656</v>
+        <v>17</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
-        <v>51</v>
-      </c>
-      <c r="B50" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="35" t="s">
-        <v>63</v>
+      <c r="A50" s="3">
+        <v>72</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>79</v>
       </c>
       <c r="E50">
-        <v>10.7967716</v>
+        <v>10.367577300000001</v>
       </c>
       <c r="F50">
-        <v>106.6627697</v>
+        <v>107.07491640000001</v>
       </c>
       <c r="G50" s="1">
-        <v>1662</v>
+        <v>534</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7">
-        <v>51</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>88</v>
+      <c r="A51" s="3">
+        <v>72</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>78</v>
       </c>
       <c r="E51">
-        <v>10.6798705</v>
+        <v>10.3924834</v>
       </c>
       <c r="F51">
-        <v>106.7478354</v>
+        <v>107.127064</v>
       </c>
       <c r="G51" s="1">
-        <v>1840</v>
+        <v>299</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7">
-        <v>51</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>104</v>
+      <c r="A52" s="3">
+        <v>72</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>136</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="1">
-        <v>11.4531648</v>
-      </c>
-      <c r="F52" s="1">
-        <v>106.7753458</v>
+        <v>13</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52">
+        <v>10.509597100000001</v>
+      </c>
+      <c r="F52">
+        <v>107.19429890000001</v>
       </c>
       <c r="G52" s="1">
-        <v>1841</v>
+        <v>786</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
-        <v>51</v>
-      </c>
-      <c r="B53" s="25" t="s">
-        <v>106</v>
+      <c r="A53" s="3">
+        <v>72</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>139</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53">
-        <v>10.781197199999999</v>
-      </c>
-      <c r="F53">
-        <v>106.75778560000001</v>
+        <v>14</v>
+      </c>
+      <c r="D53" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" s="1">
+        <v>10.597046799999999</v>
+      </c>
+      <c r="F53" s="1">
+        <v>107.05596540000001</v>
       </c>
       <c r="G53" s="1">
-        <v>1943</v>
+        <v>625</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
-        <v>51</v>
-      </c>
-      <c r="B54" s="25" t="s">
-        <v>95</v>
+      <c r="A54" s="3">
+        <v>72</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>140</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54">
-        <v>10.367577300000001</v>
-      </c>
-      <c r="F54">
-        <v>107.07491640000001</v>
+        <v>15</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" s="1">
+        <v>10.59721</v>
+      </c>
+      <c r="F54" s="1">
+        <v>106.9759614</v>
       </c>
       <c r="G54" s="1">
-        <v>2038</v>
+        <v>295</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="7">
-        <v>51</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>146</v>
+      <c r="A55" s="3">
+        <v>72</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E55">
-        <v>10.509597100000001</v>
-      </c>
-      <c r="F55">
-        <v>107.19429890000001</v>
+        <v>18</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E55" s="1">
+        <v>10.697192599999999</v>
+      </c>
+      <c r="F55" s="1">
+        <v>107.2904827</v>
       </c>
       <c r="G55" s="1">
-        <v>2326</v>
+        <v>87</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -2250,23 +2274,19 @@
       <c r="A56" s="7">
         <v>51</v>
       </c>
-      <c r="B56" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="B56" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="4"/>
       <c r="E56" s="1">
-        <v>10.767180400000001</v>
+        <v>10.797376</v>
       </c>
       <c r="F56" s="1">
-        <v>106.6643491</v>
+        <v>106.6599927</v>
       </c>
       <c r="G56" s="1">
-        <v>2345</v>
+        <v>1503</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -2275,15 +2295,11 @@
       <c r="A57" s="7">
         <v>51</v>
       </c>
-      <c r="B57" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="B57" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="4"/>
       <c r="E57" s="1">
         <v>10.7457928</v>
       </c>
@@ -2291,7 +2307,7 @@
         <v>106.66039960000001</v>
       </c>
       <c r="G57" s="1">
-        <v>2441</v>
+        <v>301</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -2300,23 +2316,19 @@
       <c r="A58" s="7">
         <v>51</v>
       </c>
-      <c r="B58" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="B58" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4"/>
       <c r="E58" s="1">
-        <v>10.597046799999999</v>
+        <v>10.8675332</v>
       </c>
       <c r="F58" s="1">
-        <v>107.05596540000001</v>
+        <v>106.63021790000001</v>
       </c>
       <c r="G58" s="1">
-        <v>2806</v>
+        <v>267</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -2325,98 +2337,82 @@
       <c r="A59" s="7">
         <v>51</v>
       </c>
-      <c r="B59" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B59" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="4"/>
       <c r="E59" s="1">
-        <v>10.8675332</v>
+        <v>10.767180400000001</v>
       </c>
       <c r="F59" s="1">
-        <v>106.63021790000001</v>
+        <v>106.6643491</v>
       </c>
       <c r="G59" s="1">
-        <v>2877</v>
+        <v>21</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60">
-        <v>10.9083784</v>
-      </c>
-      <c r="F60">
-        <v>106.6923918</v>
+        <v>133</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="1">
+        <v>11.4531648</v>
+      </c>
+      <c r="F60" s="1">
+        <v>106.7753458</v>
       </c>
       <c r="G60" s="1">
-        <v>2930</v>
+        <v>78</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>52</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="4"/>
       <c r="E61" s="1">
-        <v>10.5388123</v>
+        <v>11.242782200000001</v>
       </c>
       <c r="F61" s="1">
-        <v>107.4099504</v>
+        <v>106.73288789999999</v>
       </c>
       <c r="G61" s="1">
-        <v>2979</v>
+        <v>44</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E62">
-        <v>10.7531734</v>
-      </c>
-      <c r="F62">
-        <v>106.6784356</v>
+        <v>141</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="1">
+        <v>10.5388123</v>
+      </c>
+      <c r="F62" s="1">
+        <v>107.4099504</v>
       </c>
       <c r="G62" s="1">
-        <v>2999</v>
+        <v>147</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -12498,13 +12494,9 @@
       <c r="I978" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G62" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">
-      <sortCondition ref="G1:G62"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:D40" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">
-    <sortCondition ref="G1:G62"/>
+    <sortCondition ref="A1:A62"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
